--- a/tables/main/r2_income_all_regions.xlsx
+++ b/tables/main/r2_income_all_regions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">indicator</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t xml:space="preserve">Region: continents (5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region: UN sub-regions</t>
   </si>
   <si>
     <t xml:space="preserve">Happy</t>
@@ -452,13 +449,10 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>0.14383463224282</v>
@@ -496,13 +490,10 @@
       <c r="M2" t="n">
         <v>0.0819477344673852</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.299355078350836</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="n">
         <v>0.0000209961399793013</v>
@@ -540,13 +531,10 @@
       <c r="M3" t="n">
         <v>0.233360482813203</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.457123742975876</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
         <v>0.07174286871262</v>
@@ -584,13 +572,10 @@
       <c r="M4" t="n">
         <v>0.098293512189043</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.223659519226086</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="n">
         <v>0.00351087463402411</v>
@@ -628,13 +613,10 @@
       <c r="M5" t="n">
         <v>0.217134085878367</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.449556965915496</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="n">
         <v>0.0443332739388511</v>
@@ -672,13 +654,10 @@
       <c r="M6" t="n">
         <v>0.154501749335799</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.388786987005451</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="n">
         <v>0.233399863170721</v>
@@ -716,13 +695,10 @@
       <c r="M7" t="n">
         <v>0.234790186077392</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.401916582026538</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>0.316272866956971</v>
@@ -760,13 +736,10 @@
       <c r="M8" t="n">
         <v>0.185292541167775</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.37210168231651</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>0.274835270542935</v>
@@ -804,13 +777,10 @@
       <c r="M9" t="n">
         <v>0.135537814382107</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.363912813705656</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>0.135993830792365</v>
@@ -848,13 +818,10 @@
       <c r="M10" t="n">
         <v>0.167607263288884</v>
       </c>
-      <c r="N10" t="n">
-        <v>0.369551671440306</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>0.316272866956971</v>
@@ -891,9 +858,6 @@
       </c>
       <c r="M11" t="n">
         <v>0.234790186077392</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.457123742975876</v>
       </c>
     </row>
   </sheetData>

--- a/tables/main/r2_income_all_regions.xlsx
+++ b/tables/main/r2_income_all_regions.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Region: World Bank (7)</t>
   </si>
   <si>
-    <t xml:space="preserve">Region: continents (5)</t>
+    <t xml:space="preserve">Region: continents (6)</t>
   </si>
   <si>
     <t xml:space="preserve">Happy</t>
@@ -488,7 +488,7 @@
         <v>0.111010906564617</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0819477344673852</v>
+        <v>0.0920894413401486</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +529,7 @@
         <v>0.23217511345087</v>
       </c>
       <c r="M3" t="n">
-        <v>0.233360482813203</v>
+        <v>0.234128959896389</v>
       </c>
     </row>
     <row r="4">
@@ -570,7 +570,7 @@
         <v>0.15755178520278</v>
       </c>
       <c r="M4" t="n">
-        <v>0.098293512189043</v>
+        <v>0.0991330101013062</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         <v>0.225101193368732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.217134085878367</v>
+        <v>0.217500332030212</v>
       </c>
     </row>
     <row r="6">
@@ -652,7 +652,7 @@
         <v>0.154281023410774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.154501749335799</v>
+        <v>0.155662793827058</v>
       </c>
     </row>
     <row r="7">
@@ -693,7 +693,7 @@
         <v>0.229869568355362</v>
       </c>
       <c r="M7" t="n">
-        <v>0.234790186077392</v>
+        <v>0.234855641380854</v>
       </c>
     </row>
     <row r="8">
@@ -734,7 +734,7 @@
         <v>0.204786227406024</v>
       </c>
       <c r="M8" t="n">
-        <v>0.185292541167775</v>
+        <v>0.186586790162678</v>
       </c>
     </row>
     <row r="9">
@@ -775,7 +775,7 @@
         <v>0.1714646123365</v>
       </c>
       <c r="M9" t="n">
-        <v>0.135537814382107</v>
+        <v>0.140110880071311</v>
       </c>
     </row>
     <row r="10">
@@ -816,7 +816,7 @@
         <v>0.185780053761957</v>
       </c>
       <c r="M10" t="n">
-        <v>0.167607263288884</v>
+        <v>0.170008481101245</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         <v>0.23217511345087</v>
       </c>
       <c r="M11" t="n">
-        <v>0.234790186077392</v>
+        <v>0.234855641380854</v>
       </c>
     </row>
   </sheetData>

--- a/tables/main/r2_income_all_regions.xlsx
+++ b/tables/main/r2_income_all_regions.xlsx
@@ -488,7 +488,7 @@
         <v>0.111010906564617</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0920894413401486</v>
+        <v>0.0898082386875273</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +529,7 @@
         <v>0.23217511345087</v>
       </c>
       <c r="M3" t="n">
-        <v>0.234128959896389</v>
+        <v>0.24774773010099</v>
       </c>
     </row>
     <row r="4">
@@ -570,7 +570,7 @@
         <v>0.15755178520278</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0991330101013062</v>
+        <v>0.0984902985117729</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         <v>0.225101193368732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.217500332030212</v>
+        <v>0.229562580291188</v>
       </c>
     </row>
     <row r="6">
@@ -652,7 +652,7 @@
         <v>0.154281023410774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.155662793827058</v>
+        <v>0.166680433222706</v>
       </c>
     </row>
     <row r="7">
@@ -693,7 +693,7 @@
         <v>0.229869568355362</v>
       </c>
       <c r="M7" t="n">
-        <v>0.234855641380854</v>
+        <v>0.237243716184806</v>
       </c>
     </row>
     <row r="8">
@@ -734,7 +734,7 @@
         <v>0.204786227406024</v>
       </c>
       <c r="M8" t="n">
-        <v>0.186586790162678</v>
+        <v>0.186786758590563</v>
       </c>
     </row>
     <row r="9">
@@ -775,7 +775,7 @@
         <v>0.1714646123365</v>
       </c>
       <c r="M9" t="n">
-        <v>0.140110880071311</v>
+        <v>0.139736629094961</v>
       </c>
     </row>
     <row r="10">
@@ -816,7 +816,7 @@
         <v>0.185780053761957</v>
       </c>
       <c r="M10" t="n">
-        <v>0.170008481101245</v>
+        <v>0.174507048085564</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         <v>0.23217511345087</v>
       </c>
       <c r="M11" t="n">
-        <v>0.234855641380854</v>
+        <v>0.24774773010099</v>
       </c>
     </row>
   </sheetData>
